--- a/artfynd/A 36209-2021 artfynd.xlsx
+++ b/artfynd/A 36209-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 36209-2021 artfynd.xlsx
+++ b/artfynd/A 36209-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>5286655</v>
       </c>
       <c r="B2" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -729,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560003.9489252452</v>
+        <v>560004</v>
       </c>
       <c r="R2" t="n">
-        <v>6596268.128946437</v>
+        <v>6596268</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -762,19 +757,9 @@
           <t>2012-05-22</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-05-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -809,12 +794,7 @@
         <v>5286656</v>
       </c>
       <c r="B3" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -860,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>559850.2132913683</v>
+        <v>559850</v>
       </c>
       <c r="R3" t="n">
-        <v>6596275.329616573</v>
+        <v>6596275</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -893,19 +873,9 @@
           <t>2012-05-22</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2012-05-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,6 +904,1050 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5286657</v>
+      </c>
+      <c r="B4" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Norsa, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>559833</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6596277</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Munktorp</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2012-05-22</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2012-05-22</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Hans Klinga</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Hans Klinga</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5286658</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Norsa, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>559819</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6596282</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Munktorp</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2012-05-22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2012-05-22</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Hans Klinga</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Hans Klinga</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5286659</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Norsa, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>559831</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6596280</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Munktorp</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2012-05-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2012-05-22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Hans Klinga</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Hans Klinga</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5286660</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Norsa, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>559833</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6596286</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Munktorp</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2012-05-22</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2012-05-22</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Hans Klinga</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Hans Klinga</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5286662</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Norsa, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>559816</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6596288</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Munktorp</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2012-05-22</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2012-05-22</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Hans Klinga</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Hans Klinga</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>5286663</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Norsa, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>559828</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6596283</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Munktorp</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2012-05-22</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2012-05-22</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Hans Klinga</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Hans Klinga</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5286664</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Norsa, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>559819</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6596279</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Munktorp</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2012-05-22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2012-05-22</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Hans Klinga</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Hans Klinga</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>5286665</v>
+      </c>
+      <c r="B11" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Norsa, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>559822</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6596279</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Munktorp</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2012-05-22</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2012-05-22</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Hans Klinga</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Hans Klinga</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>5287754</v>
+      </c>
+      <c r="B12" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Norsa, Skogen i ostligaste delen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>560003</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6596075</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Munktorp</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2012-07-16</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2012-07-16</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Em blommande, en i frukt</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Lasse Gustavsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Lasse Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
